--- a/Output Files Qwen3.5 9B/metrics_summary_qwen.xlsx
+++ b/Output Files Qwen3.5 9B/metrics_summary_qwen.xlsx
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4.94</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="180">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0.0103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0.0103</v>
+        <v>0.0051</v>
       </c>
     </row>
     <row r="184">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">

--- a/Output Files Qwen3.5 9B/metrics_summary_qwen.xlsx
+++ b/Output Files Qwen3.5 9B/metrics_summary_qwen.xlsx
@@ -451,11 +451,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>match_content</t>
+          <t>energy_cost_MAE</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>195</v>
+        <v>0.2434</v>
       </c>
     </row>
     <row r="3">
@@ -471,11 +471,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>match_no_match</t>
+          <t>energy_cost_RMSE</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.2952</v>
       </c>
     </row>
     <row r="4">
@@ -491,11 +491,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>diag_files_loaded</t>
+          <t>environmental_MAE</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="5">
@@ -511,11 +511,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>diag_total_scenarios</t>
+          <t>environmental_RMSE</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>975</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="6">
@@ -531,11 +531,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>diag_failed_scenarios</t>
+          <t>comfort_MAE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0.1829</v>
       </c>
     </row>
     <row r="7">
@@ -551,11 +551,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>diag_successful_scenarios</t>
+          <t>comfort_RMSE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>973</v>
+        <v>0.2341</v>
       </c>
     </row>
     <row r="8">
@@ -571,11 +571,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>diag_failed_calls</t>
+          <t>practicality_MAE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.1967</v>
       </c>
     </row>
     <row r="9">
@@ -591,11 +591,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>diag_successful_calls</t>
+          <t>practicality_RMSE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2923</v>
+        <v>0.2539</v>
       </c>
     </row>
     <row r="10">
@@ -611,11 +611,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>diag_EXTRACTION_INVALID_JSON</t>
+          <t>overall_MAE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.2215</v>
       </c>
     </row>
     <row r="11">
@@ -631,11 +631,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>diag_FAILED_MISSING_SCORE</t>
+          <t>overall_RMSE</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.2787</v>
       </c>
     </row>
     <row r="12">
@@ -651,11 +651,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>diag_FAILED_OUT_OF_BOUNDS</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.0017</v>
       </c>
     </row>
     <row r="13">
@@ -671,11 +671,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>diag_FAILED_INVALID_SCORE_TYPE</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
     </row>
     <row r="14">
@@ -691,11 +691,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>diag_FAILED_API_EXHAUSTED</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.3179</v>
       </c>
     </row>
     <row r="15">
@@ -711,11 +711,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>diag_FAILED_UNKNOWN</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="16">
@@ -731,11 +731,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>n_runs</t>
+          <t>n_scenarios_evaluated</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17">
@@ -746,16 +746,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>n_successful_runs_mean</t>
+          <t>energy_cost_MAE</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4.99</v>
+        <v>0.2335</v>
       </c>
     </row>
     <row r="18">
@@ -766,16 +766,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>n_failed_scenarios</t>
+          <t>energy_cost_RMSE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.2757</v>
       </c>
     </row>
     <row r="19">
@@ -786,16 +786,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>n_total_arch_scenarios</t>
+          <t>environmental_MAE</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>195</v>
+        <v>0.2327</v>
       </c>
     </row>
     <row r="20">
@@ -806,16 +806,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>total_failure_rate</t>
+          <t>environmental_RMSE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.2742</v>
       </c>
     </row>
     <row r="21">
@@ -826,16 +826,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>comfort_MAE</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.2434</v>
+        <v>0.1975</v>
       </c>
     </row>
     <row r="22">
@@ -846,16 +846,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>comfort_RMSE</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.2952</v>
+        <v>0.2466</v>
       </c>
     </row>
     <row r="23">
@@ -866,16 +866,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>practicality_MAE</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.263</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="24">
@@ -886,16 +886,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>practicality_RMSE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.323</v>
+        <v>0.1591</v>
       </c>
     </row>
     <row r="25">
@@ -906,16 +906,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>overall_MAE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1829</v>
+        <v>0.1962</v>
       </c>
     </row>
     <row r="26">
@@ -926,16 +926,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>overall_RMSE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.2341</v>
+        <v>0.2436</v>
       </c>
     </row>
     <row r="27">
@@ -946,16 +946,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.1967</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="28">
@@ -966,16 +966,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.2539</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="29">
@@ -986,16 +986,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.2215</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="30">
@@ -1006,16 +1006,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.2787</v>
+        <v>0.6714</v>
       </c>
     </row>
     <row r="31">
@@ -1026,16 +1026,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>n_scenarios_evaluated</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.0017</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32">
@@ -1046,16 +1046,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>energy_cost_MAE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.0051</v>
+        <v>0.3034</v>
       </c>
     </row>
     <row r="33">
@@ -1066,16 +1066,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>energy_cost_RMSE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.3179</v>
+        <v>0.3541</v>
       </c>
     </row>
     <row r="34">
@@ -1086,16 +1086,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>environmental_MAE</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.641</v>
+        <v>0.3679</v>
       </c>
     </row>
     <row r="35">
@@ -1106,16 +1106,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>environmental_RMSE</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>195</v>
+        <v>0.4246</v>
       </c>
     </row>
     <row r="36">
@@ -1126,16 +1126,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>comfort_MAE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.2335</v>
+        <v>0.1893</v>
       </c>
     </row>
     <row r="37">
@@ -1146,16 +1146,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>comfort_RMSE</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.2757</v>
+        <v>0.2383</v>
       </c>
     </row>
     <row r="38">
@@ -1166,16 +1166,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>practicality_MAE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.2327</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="39">
@@ -1186,16 +1186,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>practicality_RMSE</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.2742</v>
+        <v>0.2885</v>
       </c>
     </row>
     <row r="40">
@@ -1206,16 +1206,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>overall_MAE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.1975</v>
+        <v>0.2751</v>
       </c>
     </row>
     <row r="41">
@@ -1226,16 +1226,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>overall_RMSE</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.2466</v>
+        <v>0.3338</v>
       </c>
     </row>
     <row r="42">
@@ -1246,16 +1246,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.121</v>
+        <v>-0.1282</v>
       </c>
     </row>
     <row r="43">
@@ -1266,16 +1266,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.1591</v>
+        <v>-0.1231</v>
       </c>
     </row>
     <row r="44">
@@ -1286,16 +1286,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.1962</v>
+        <v>0.2154</v>
       </c>
     </row>
     <row r="45">
@@ -1306,16 +1306,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2436</v>
+        <v>0.5846</v>
       </c>
     </row>
     <row r="46">
@@ -1326,16 +1326,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>n_scenarios_evaluated</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.0571</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47">
@@ -1346,16 +1346,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>energy_cost_MAE</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.0429</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="48">
@@ -1366,16 +1366,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>energy_cost_RMSE</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.4</v>
+        <v>0.2423</v>
       </c>
     </row>
     <row r="49">
@@ -1386,16 +1386,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>environmental_MAE</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.6714</v>
+        <v>0.1849</v>
       </c>
     </row>
     <row r="50">
@@ -1406,16 +1406,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>environmental_RMSE</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>70</v>
+        <v>0.2365</v>
       </c>
     </row>
     <row r="51">
@@ -1426,16 +1426,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>comfort_MAE</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.3034</v>
+        <v>0.1591</v>
       </c>
     </row>
     <row r="52">
@@ -1446,16 +1446,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>comfort_RMSE</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.3541</v>
+        <v>0.2137</v>
       </c>
     </row>
     <row r="53">
@@ -1466,16 +1466,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>practicality_MAE</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.3679</v>
+        <v>0.2382</v>
       </c>
     </row>
     <row r="54">
@@ -1486,16 +1486,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>practicality_RMSE</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.4246</v>
+        <v>0.2996</v>
       </c>
     </row>
     <row r="55">
@@ -1506,16 +1506,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>overall_MAE</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.1893</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="56">
@@ -1526,16 +1526,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>overall_RMSE</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.2383</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="57">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.24</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="58">
@@ -1566,16 +1566,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.2885</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="59">
@@ -1586,16 +1586,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.2751</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="60">
@@ -1606,16 +1606,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.3338</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="61">
@@ -1626,396 +1626,396 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>n_scenarios_evaluated</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-0.1282</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>energy_cost_MAE</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-0.1231</v>
+        <v>0.1705</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>energy_cost_RMSE</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.2154</v>
+        <v>0.2303</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>environmental_MAE</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.5846</v>
+        <v>0.1687</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>environmental_RMSE</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>65</v>
+        <v>0.2312</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>comfort_MAE</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.1899</v>
+        <v>0.1573</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>comfort_RMSE</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.2423</v>
+        <v>0.2229</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>practicality_MAE</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.1849</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>practicality_RMSE</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.2365</v>
+        <v>0.1979</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>overall_MAE</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.1591</v>
+        <v>0.1589</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>overall_RMSE</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.2137</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.2382</v>
+        <v>0.2821</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.2996</v>
+        <v>0.3231</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.193</v>
+        <v>0.5128</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.25</v>
+        <v>0.7949000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>n_scenarios_evaluated</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0667</v>
+        <v>195</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>energy_cost_MAE</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.1</v>
+        <v>0.2002</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>energy_cost_RMSE</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.3333</v>
+        <v>0.2581</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>environmental_MAE</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.6667</v>
+        <v>0.1998</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>environmental_RMSE</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>60</v>
+        <v>0.2563</v>
       </c>
     </row>
     <row r="81">
@@ -2026,16 +2026,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>match_content</t>
+          <t>comfort_MAE</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>195</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="82">
@@ -2046,16 +2046,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>match_no_match</t>
+          <t>comfort_RMSE</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="83">
@@ -2066,16 +2066,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>diag_files_loaded</t>
+          <t>practicality_MAE</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -2086,16 +2086,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>diag_total_scenarios</t>
+          <t>practicality_RMSE</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>975</v>
+        <v>0.1329</v>
       </c>
     </row>
     <row r="85">
@@ -2106,16 +2106,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>diag_failed_scenarios</t>
+          <t>overall_MAE</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="86">
@@ -2126,16 +2126,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>diag_successful_scenarios</t>
+          <t>overall_RMSE</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>975</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="87">
@@ -2146,16 +2146,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>diag_failed_calls</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>0.1905</v>
       </c>
     </row>
     <row r="88">
@@ -2166,16 +2166,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>diag_successful_calls</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2925</v>
+        <v>0.2357</v>
       </c>
     </row>
     <row r="89">
@@ -2186,16 +2186,16 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>diag_EXTRACTION_INVALID_JSON</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>0.4429</v>
       </c>
     </row>
     <row r="90">
@@ -2206,16 +2206,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>diag_FAILED_MISSING_SCORE</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>0.7286</v>
       </c>
     </row>
     <row r="91">
@@ -2226,16 +2226,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>diag_FAILED_OUT_OF_BOUNDS</t>
+          <t>n_scenarios_evaluated</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92">
@@ -2246,16 +2246,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>diag_FAILED_INVALID_SCORE_TYPE</t>
+          <t>energy_cost_MAE</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>0.1546</v>
       </c>
     </row>
     <row r="93">
@@ -2266,16 +2266,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>diag_FAILED_API_EXHAUSTED</t>
+          <t>energy_cost_RMSE</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>0.2137</v>
       </c>
     </row>
     <row r="94">
@@ -2286,16 +2286,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>diag_FAILED_UNKNOWN</t>
+          <t>environmental_MAE</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>0.1514</v>
       </c>
     </row>
     <row r="95">
@@ -2306,16 +2306,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>n_runs</t>
+          <t>environmental_RMSE</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>0.2182</v>
       </c>
     </row>
     <row r="96">
@@ -2326,16 +2326,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>n_successful_runs_mean</t>
+          <t>comfort_MAE</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>0.2098</v>
       </c>
     </row>
     <row r="97">
@@ -2346,16 +2346,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>n_failed_scenarios</t>
+          <t>comfort_RMSE</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>0.2655</v>
       </c>
     </row>
     <row r="98">
@@ -2366,16 +2366,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>n_total_arch_scenarios</t>
+          <t>practicality_MAE</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>195</v>
+        <v>0.1988</v>
       </c>
     </row>
     <row r="99">
@@ -2386,16 +2386,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>total_failure_rate</t>
+          <t>practicality_RMSE</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>0.2606</v>
       </c>
     </row>
     <row r="100">
@@ -2406,16 +2406,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>overall_MAE</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.1705</v>
+        <v>0.1786</v>
       </c>
     </row>
     <row r="101">
@@ -2426,16 +2426,16 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>overall_RMSE</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.2303</v>
+        <v>0.2407</v>
       </c>
     </row>
     <row r="102">
@@ -2446,16 +2446,16 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.1687</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="103">
@@ -2466,16 +2466,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.2312</v>
+        <v>0.2769</v>
       </c>
     </row>
     <row r="104">
@@ -2486,16 +2486,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.1573</v>
+        <v>0.5077</v>
       </c>
     </row>
     <row r="105">
@@ -2506,16 +2506,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.2229</v>
+        <v>0.8308</v>
       </c>
     </row>
     <row r="106">
@@ -2526,16 +2526,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>n_scenarios_evaluated</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.139</v>
+        <v>65</v>
       </c>
     </row>
     <row r="107">
@@ -2546,16 +2546,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>energy_cost_MAE</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.1979</v>
+        <v>0.1529</v>
       </c>
     </row>
     <row r="108">
@@ -2566,16 +2566,16 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>energy_cost_RMSE</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.1589</v>
+        <v>0.2126</v>
       </c>
     </row>
     <row r="109">
@@ -2586,16 +2586,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>environmental_MAE</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.221</v>
+        <v>0.1513</v>
       </c>
     </row>
     <row r="110">
@@ -2606,16 +2606,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>environmental_RMSE</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.2821</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="111">
@@ -2626,16 +2626,16 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>comfort_MAE</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.3231</v>
+        <v>0.1172</v>
       </c>
     </row>
     <row r="112">
@@ -2646,16 +2646,16 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>comfort_RMSE</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.5128</v>
+        <v>0.2006</v>
       </c>
     </row>
     <row r="113">
@@ -2666,16 +2666,16 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>practicality_MAE</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.1327</v>
       </c>
     </row>
     <row r="114">
@@ -2686,16 +2686,16 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>practicality_RMSE</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>195</v>
+        <v>0.1818</v>
       </c>
     </row>
     <row r="115">
@@ -2706,16 +2706,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>overall_MAE</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.2002</v>
+        <v>0.1385</v>
       </c>
     </row>
     <row r="116">
@@ -2726,16 +2726,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>overall_RMSE</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.2581</v>
+        <v>0.2025</v>
       </c>
     </row>
     <row r="117">
@@ -2746,16 +2746,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.1998</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="118">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.2563</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="119">
@@ -2786,16 +2786,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.143</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="120">
@@ -2806,16 +2806,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.196</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="121">
@@ -2826,776 +2826,776 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>n_scenarios_evaluated</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.08890000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>energy_cost_MAE</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.1329</v>
+        <v>0.1045</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>energy_cost_RMSE</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.158</v>
+        <v>0.1759</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>environmental_MAE</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.217</v>
+        <v>0.1413</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>environmental_RMSE</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.1905</v>
+        <v>0.2412</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>comfort_MAE</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.2357</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>comfort_RMSE</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.4429</v>
+        <v>0.0356</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>practicality_MAE</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.7286</v>
+        <v>0.0164</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>practicality_RMSE</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>70</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>overall_MAE</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.1546</v>
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>overall_RMSE</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.2137</v>
+        <v>0.1525</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.1514</v>
+        <v>0.8769</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.2182</v>
+        <v>0.8872</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.2098</v>
+        <v>0.9026</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.2655</v>
+        <v>0.9641</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>n_scenarios_evaluated</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.1988</v>
+        <v>195</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>energy_cost_MAE</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.2606</v>
+        <v>0.08749999999999999</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>energy_cost_RMSE</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.1786</v>
+        <v>0.1311</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>environmental_MAE</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.2407</v>
+        <v>0.0842</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>environmental_RMSE</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.241</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>comfort_MAE</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.2769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>comfort_RMSE</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.5077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>practicality_MAE</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.8308</v>
+        <v>0.0237</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>practicality_RMSE</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>65</v>
+        <v>0.0305</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>overall_MAE</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.1529</v>
+        <v>0.0488</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>overall_RMSE</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.2126</v>
+        <v>0.0915</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.1513</v>
+        <v>0.8762</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.2132</v>
+        <v>0.8929</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.1172</v>
+        <v>0.8571</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.2006</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>n_scenarios_evaluated</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.1327</v>
+        <v>70</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>energy_cost_MAE</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.1818</v>
+        <v>0.1727</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>energy_cost_RMSE</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.1385</v>
+        <v>0.2551</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>environmental_MAE</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.2025</v>
+        <v>0.2879</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>environmental_RMSE</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.4333</v>
+        <v>0.3861</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>comfort_MAE</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.475</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>comfort_RMSE</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.6</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>practicality_MAE</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.8333</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>practicality_RMSE</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>60</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="160">
@@ -3606,16 +3606,16 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>match_content</t>
+          <t>overall_MAE</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>195</v>
+        <v>0.1153</v>
       </c>
     </row>
     <row r="161">
@@ -3626,16 +3626,16 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>match_no_match</t>
+          <t>overall_RMSE</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>0.2314</v>
       </c>
     </row>
     <row r="162">
@@ -3646,16 +3646,16 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>diag_files_loaded</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>5</v>
+        <v>0.8974</v>
       </c>
     </row>
     <row r="163">
@@ -3666,16 +3666,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>diag_total_scenarios</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>975</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="164">
@@ -3686,16 +3686,16 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>diag_failed_scenarios</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>2</v>
+        <v>0.9385</v>
       </c>
     </row>
     <row r="165">
@@ -3706,16 +3706,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>diag_successful_scenarios</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>973</v>
+        <v>0.9692</v>
       </c>
     </row>
     <row r="166">
@@ -3726,16 +3726,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>diag_failed_calls</t>
+          <t>n_scenarios_evaluated</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="167">
@@ -3746,16 +3746,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>diag_successful_calls</t>
+          <t>energy_cost_MAE</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>973</v>
+        <v>0.0503</v>
       </c>
     </row>
     <row r="168">
@@ -3766,16 +3766,16 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>diag_FAILED_EXTRACTION_NON_JSON_WRAPPER</t>
+          <t>energy_cost_RMSE</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>0.1003</v>
       </c>
     </row>
     <row r="169">
@@ -3786,16 +3786,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>diag_EXTRACTION_INVALID_JSON</t>
+          <t>environmental_MAE</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>0.0493</v>
       </c>
     </row>
     <row r="170">
@@ -3806,16 +3806,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>diag_FAILED_EXTRACTION_INVALID_DECISION_TYPE</t>
+          <t>environmental_RMSE</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>0.0982</v>
       </c>
     </row>
     <row r="171">
@@ -3826,16 +3826,16 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>diag_FAILED_EXTRACTION_INVALID_CALCULATOR</t>
+          <t>comfort_MAE</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>0.0271</v>
       </c>
     </row>
     <row r="172">
@@ -3846,16 +3846,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>diag_FAILED_EXTRACTION_MISSING_PARAMETERS</t>
+          <t>comfort_RMSE</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="173">
@@ -3866,16 +3866,16 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>diag_FAILED_EXTRACTION_EXCEPTION</t>
+          <t>practicality_MAE</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="174">
@@ -3886,16 +3886,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>diag_FAILED_GROUND_TRUTH_CALCULATION_EXCEPTION</t>
+          <t>practicality_RMSE</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0</v>
+        <v>0.0851</v>
       </c>
     </row>
     <row r="175">
@@ -3906,16 +3906,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>diag_FAILED_GROUND_TRUTH_MISSING_KEY</t>
+          <t>overall_MAE</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="176">
@@ -3926,16 +3926,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>diag_FAILED_API_EXHAUSTED</t>
+          <t>overall_RMSE</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>0.0881</v>
       </c>
     </row>
     <row r="177">
@@ -3946,16 +3946,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>diag_FAILED_UNKNOWN</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>0.8556</v>
       </c>
     </row>
     <row r="178">
@@ -3966,16 +3966,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>n_runs</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5</v>
+        <v>0.8667</v>
       </c>
     </row>
     <row r="179">
@@ -3986,16 +3986,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>n_successful_runs_mean</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4.99</v>
+        <v>0.9167</v>
       </c>
     </row>
     <row r="180">
@@ -4006,16 +4006,16 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>n_failed_scenarios</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="181">
@@ -4026,22 +4026,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>n_total_arch_scenarios</t>
+          <t>n_scenarios_evaluated</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>195</v>
+        <v>60</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4051,17 +4051,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>total_failure_rate</t>
+          <t>match_content</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4071,17 +4071,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>extraction_failure_rate</t>
+          <t>match_no_match</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0.0051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>calculation_failure_rate</t>
+          <t>diag_files_loaded</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>n_extraction_failures</t>
+          <t>diag_total_scenarios</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>975</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>n_calculation_failures</t>
+          <t>diag_failed_scenarios</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>diag_successful_scenarios</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0.1045</v>
+        <v>973</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>diag_failed_calls</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.1759</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4191,17 +4191,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>diag_successful_calls</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.1413</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>diag_EXTRACTION_INVALID_JSON</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.2412</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>diag_FAILED_MISSING_SCORE</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.008399999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4251,17 +4251,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>diag_FAILED_OUT_OF_BOUNDS</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0.0356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>diag_FAILED_INVALID_SCORE_TYPE</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.0164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>diag_FAILED_API_EXHAUSTED</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0.0507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4311,17 +4311,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>diag_FAILED_UNKNOWN</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0.06759999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>n_runs</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0.1525</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>n_successful_runs_mean</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.8769</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4371,17 +4371,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>n_failed_scenarios</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0.8872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>n_total_arch_scenarios</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0.9026</v>
+        <v>195</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>total_failure_rate</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.9641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>match_content</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -4441,117 +4441,117 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>match_no_match</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.08749999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>diag_files_loaded</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.1311</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>diag_total_scenarios</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.0842</v>
+        <v>975</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>diag_failed_scenarios</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>diag_successful_scenarios</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>diag_failed_calls</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -4561,241 +4561,241 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>diag_successful_calls</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0.0237</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>diag_EXTRACTION_INVALID_JSON</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.0305</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>diag_FAILED_MISSING_SCORE</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0.0488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>diag_FAILED_OUT_OF_BOUNDS</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0.0915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>diag_FAILED_INVALID_SCORE_TYPE</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0.8762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>diag_FAILED_API_EXHAUSTED</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.8929</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>diag_FAILED_UNKNOWN</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.8571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>n_runs</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.9714</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>n_successful_runs_mean</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>n_failed_scenarios</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0.1727</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>n_total_arch_scenarios</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>0.2551</v>
+        <v>195</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>total_failure_rate</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>0.2879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -4806,16 +4806,16 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>match_content</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0.3861</v>
+        <v>195</v>
       </c>
     </row>
     <row r="221">
@@ -4826,16 +4826,16 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>match_no_match</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -4846,16 +4846,16 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>diag_files_loaded</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.0014</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223">
@@ -4866,16 +4866,16 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>diag_total_scenarios</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.0002</v>
+        <v>975</v>
       </c>
     </row>
     <row r="224">
@@ -4886,16 +4886,16 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>diag_failed_scenarios</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0.002</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -4906,16 +4906,16 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>diag_successful_scenarios</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.1153</v>
+        <v>973</v>
       </c>
     </row>
     <row r="226">
@@ -4926,16 +4926,16 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>diag_failed_calls</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0.2314</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -4946,16 +4946,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>diag_successful_calls</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.8974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="228">
@@ -4966,16 +4966,16 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>diag_FAILED_EXTRACTION_NON_JSON_WRAPPER</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -4986,16 +4986,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>diag_EXTRACTION_INVALID_JSON</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0.9385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -5006,16 +5006,16 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>diag_FAILED_EXTRACTION_INVALID_DECISION_TYPE</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>0.9692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -5026,16 +5026,16 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>diag_FAILED_EXTRACTION_INVALID_CALCULATOR</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -5046,16 +5046,16 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>diag_FAILED_EXTRACTION_MISSING_PARAMETERS</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>0.0503</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -5066,16 +5066,16 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>diag_FAILED_EXTRACTION_EXCEPTION</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>0.1003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -5086,16 +5086,16 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>diag_FAILED_GROUND_TRUTH_CALCULATION_EXCEPTION</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0.0493</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -5106,16 +5106,16 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>diag_FAILED_GROUND_TRUTH_MISSING_KEY</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0.0982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -5126,16 +5126,16 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>diag_FAILED_API_EXHAUSTED</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0.0271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -5146,16 +5146,16 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>diag_FAILED_UNKNOWN</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>0.06419999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -5166,16 +5166,16 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>n_runs</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0.0252</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239">
@@ -5186,16 +5186,16 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>n_successful_runs_mean</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>0.0851</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="240">
@@ -5206,16 +5206,16 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>n_failed_scenarios</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -5226,16 +5226,16 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>n_total_arch_scenarios</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0.0881</v>
+        <v>195</v>
       </c>
     </row>
     <row r="242">
@@ -5246,16 +5246,16 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>total_failure_rate</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0.8556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -5266,16 +5266,16 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>extraction_failure_rate</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0.8667</v>
+        <v>0.0051</v>
       </c>
     </row>
     <row r="244">
@@ -5286,16 +5286,16 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>calculation_failure_rate</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>0.9167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -5306,16 +5306,16 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>n_extraction_failures</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -5326,16 +5326,16 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>n_calculation_failures</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Output Files Qwen3.5 9B/metrics_summary_qwen.xlsx
+++ b/Output Files Qwen3.5 9B/metrics_summary_qwen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D246"/>
+  <dimension ref="A1:D270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4421,7 +4421,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4431,17 +4431,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>match_content</t>
+          <t>cross_criterion_rho_overall</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>195</v>
+        <v>0.9202</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>match_no_match</t>
+          <t>cross_criterion_rho_pvalue</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -4461,7 +4461,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>diag_files_loaded</t>
+          <t>cross_criterion_rho_HVAC</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>5</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4491,17 +4491,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>diag_total_scenarios</t>
+          <t>cross_criterion_rho_HVAC_pvalue</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>diag_failed_scenarios</t>
+          <t>cross_criterion_rho_Appliance</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0</v>
+        <v>0.8988</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4531,17 +4531,17 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>diag_successful_scenarios</t>
+          <t>cross_criterion_rho_Appliance_pvalue</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4551,17 +4551,17 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>diag_failed_calls</t>
+          <t>cross_criterion_rho_Shower</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4571,11 +4571,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>diag_successful_calls</t>
+          <t>cross_criterion_rho_Shower_pvalue</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>2925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -4591,11 +4591,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>diag_EXTRACTION_INVALID_JSON</t>
+          <t>match_content</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="210">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>diag_FAILED_MISSING_SCORE</t>
+          <t>match_no_match</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -4631,11 +4631,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>diag_FAILED_OUT_OF_BOUNDS</t>
+          <t>diag_files_loaded</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212">
@@ -4651,11 +4651,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>diag_FAILED_INVALID_SCORE_TYPE</t>
+          <t>diag_total_scenarios</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
     </row>
     <row r="213">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>diag_FAILED_API_EXHAUSTED</t>
+          <t>diag_failed_scenarios</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -4691,11 +4691,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>diag_FAILED_UNKNOWN</t>
+          <t>diag_successful_scenarios</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
     </row>
     <row r="215">
@@ -4711,11 +4711,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>n_runs</t>
+          <t>diag_failed_calls</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -4731,11 +4731,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>n_successful_runs_mean</t>
+          <t>diag_successful_calls</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>5</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="217">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>n_failed_scenarios</t>
+          <t>diag_EXTRACTION_INVALID_JSON</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -4771,11 +4771,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>n_total_arch_scenarios</t>
+          <t>diag_FAILED_MISSING_SCORE</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>total_failure_rate</t>
+          <t>diag_FAILED_OUT_OF_BOUNDS</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -4801,7 +4801,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -4811,17 +4811,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>match_content</t>
+          <t>diag_FAILED_INVALID_SCORE_TYPE</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>match_no_match</t>
+          <t>diag_FAILED_API_EXHAUSTED</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -4841,7 +4841,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4851,17 +4851,17 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>diag_files_loaded</t>
+          <t>diag_FAILED_UNKNOWN</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -4871,17 +4871,17 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>diag_total_scenarios</t>
+          <t>n_runs</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>975</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>diag_failed_scenarios</t>
+          <t>n_successful_runs_mean</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -4911,17 +4911,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>diag_successful_scenarios</t>
+          <t>n_failed_scenarios</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>973</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>diag_failed_calls</t>
+          <t>n_total_arch_scenarios</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>2</v>
+        <v>195</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4951,17 +4951,17 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>diag_successful_calls</t>
+          <t>total_failure_rate</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>973</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -4971,17 +4971,17 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>diag_FAILED_EXTRACTION_NON_JSON_WRAPPER</t>
+          <t>cross_criterion_rho_overall</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0</v>
+        <v>0.9202</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>diag_EXTRACTION_INVALID_JSON</t>
+          <t>cross_criterion_rho_pvalue</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -5001,7 +5001,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5011,17 +5011,17 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>diag_FAILED_EXTRACTION_INVALID_DECISION_TYPE</t>
+          <t>cross_criterion_rho_HVAC</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>0</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>diag_FAILED_EXTRACTION_INVALID_CALCULATOR</t>
+          <t>cross_criterion_rho_HVAC_pvalue</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -5041,7 +5041,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>diag_FAILED_EXTRACTION_MISSING_PARAMETERS</t>
+          <t>cross_criterion_rho_Appliance</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>0</v>
+        <v>0.8988</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>diag_FAILED_EXTRACTION_EXCEPTION</t>
+          <t>cross_criterion_rho_Appliance_pvalue</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -5081,7 +5081,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5091,17 +5091,17 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>diag_FAILED_GROUND_TRUTH_CALCULATION_EXCEPTION</t>
+          <t>cross_criterion_rho_Shower</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>diag_FAILED_GROUND_TRUTH_MISSING_KEY</t>
+          <t>cross_criterion_rho_Shower_pvalue</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -5131,11 +5131,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>diag_FAILED_API_EXHAUSTED</t>
+          <t>match_content</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="237">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>diag_FAILED_UNKNOWN</t>
+          <t>match_no_match</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>n_runs</t>
+          <t>diag_files_loaded</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -5191,11 +5191,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>n_successful_runs_mean</t>
+          <t>diag_total_scenarios</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>4.99</v>
+        <v>975</v>
       </c>
     </row>
     <row r="240">
@@ -5211,11 +5211,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>n_failed_scenarios</t>
+          <t>diag_failed_scenarios</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -5231,11 +5231,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>n_total_arch_scenarios</t>
+          <t>diag_successful_scenarios</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>195</v>
+        <v>973</v>
       </c>
     </row>
     <row r="242">
@@ -5251,11 +5251,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>total_failure_rate</t>
+          <t>diag_failed_calls</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -5271,11 +5271,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>extraction_failure_rate</t>
+          <t>diag_successful_calls</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0.0051</v>
+        <v>973</v>
       </c>
     </row>
     <row r="244">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>calculation_failure_rate</t>
+          <t>diag_FAILED_EXTRACTION_NON_JSON_WRAPPER</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -5311,11 +5311,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>n_extraction_failures</t>
+          <t>diag_EXTRACTION_INVALID_JSON</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -5331,10 +5331,490 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
+          <t>diag_FAILED_EXTRACTION_INVALID_DECISION_TYPE</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>diag_FAILED_EXTRACTION_INVALID_CALCULATOR</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>diag_FAILED_EXTRACTION_MISSING_PARAMETERS</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>diag_FAILED_EXTRACTION_EXCEPTION</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>diag_FAILED_GROUND_TRUTH_CALCULATION_EXCEPTION</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>diag_FAILED_GROUND_TRUTH_MISSING_KEY</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>diag_FAILED_API_EXHAUSTED</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>diag_FAILED_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>n_runs</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>n_successful_runs_mean</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>n_failed_scenarios</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>n_total_arch_scenarios</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>total_failure_rate</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>extraction_failure_rate</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>0.0051</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>calculation_failure_rate</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>n_extraction_failures</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
           <t>n_calculation_failures</t>
         </is>
       </c>
-      <c r="D246" t="n">
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>cross_criterion_rho_overall</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>0.9202</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>cross_criterion_rho_pvalue</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>cross_criterion_rho_HVAC</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>0.9992</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>cross_criterion_rho_HVAC_pvalue</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>cross_criterion_rho_Appliance</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>0.8988</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>cross_criterion_rho_Appliance_pvalue</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>cross_criterion_rho_Shower</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>0.9661999999999999</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>cross_criterion_rho_Shower_pvalue</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Output Files Qwen3.5 9B/metrics_summary_qwen.xlsx
+++ b/Output Files Qwen3.5 9B/metrics_summary_qwen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D605"/>
+  <dimension ref="A1:D562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.9333</v>
+        <v>0.6137</v>
       </c>
     </row>
     <row r="133">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.95</v>
+        <v>0.6256</v>
       </c>
     </row>
     <row r="134">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.9571</v>
+        <v>0.7282</v>
       </c>
     </row>
     <row r="135">
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0.8615</v>
       </c>
     </row>
     <row r="136">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>70</v>
+        <v>195</v>
       </c>
     </row>
     <row r="137">
@@ -3241,12 +3241,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3259,12 +3259,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3277,12 +3277,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3295,12 +3295,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3313,12 +3313,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3331,12 +3331,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3367,12 +3367,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3385,12 +3385,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3403,12 +3403,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3421,12 +3421,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3435,18 +3435,18 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.3709</v>
+        <v>0.0974</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3455,18 +3455,18 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.3897</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3475,18 +3475,18 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.5692</v>
+        <v>0.3692</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3495,18 +3495,18 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.8051</v>
+        <v>0.6308</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3515,18 +3515,18 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>195</v>
+        <v>65</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3539,12 +3539,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3557,12 +3557,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3575,12 +3575,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3593,12 +3593,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3629,12 +3629,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3647,12 +3647,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3665,12 +3665,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3683,12 +3683,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3701,12 +3701,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3715,18 +3715,18 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.1333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3735,18 +3735,18 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.1643</v>
+        <v>0.8167</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -3755,18 +3755,18 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.4286</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -3775,18 +3775,18 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.7143</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="182">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0.2923</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="193">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.3</v>
+        <v>0.3897</v>
       </c>
     </row>
     <row r="194">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0.5538</v>
+        <v>0.5692</v>
       </c>
     </row>
     <row r="195">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0.7692</v>
+        <v>0.8051</v>
       </c>
     </row>
     <row r="196">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
     </row>
     <row r="197">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0.7333</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="208">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0.75</v>
+        <v>0.1643</v>
       </c>
     </row>
     <row r="209">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.75</v>
+        <v>0.4286</v>
       </c>
     </row>
     <row r="210">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0.95</v>
+        <v>0.7143</v>
       </c>
     </row>
     <row r="211">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4355,18 +4355,18 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4379,12 +4379,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4397,12 +4397,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4415,12 +4415,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4433,12 +4433,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4451,12 +4451,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4469,12 +4469,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4487,12 +4487,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4505,12 +4505,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4523,12 +4523,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4541,12 +4541,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4555,18 +4555,18 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.9596</v>
+        <v>0.2923</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4575,18 +4575,18 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.9636</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4595,18 +4595,18 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0.9692</v>
+        <v>0.5538</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4615,18 +4615,18 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.9949</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4635,18 +4635,18 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>195</v>
+        <v>65</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4659,12 +4659,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4677,12 +4677,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -4695,12 +4695,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -4713,12 +4713,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -4731,12 +4731,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -4749,12 +4749,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -4767,12 +4767,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -4785,12 +4785,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -4803,12 +4803,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -4821,12 +4821,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -4835,18 +4835,18 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1</v>
+        <v>0.7333</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -4855,18 +4855,18 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -4875,18 +4875,18 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -4895,18 +4895,18 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -4915,18 +4915,18 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -4934,17 +4934,19 @@
           <t>energy_cost_MAE</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="n">
+        <v>0.2434</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -4952,17 +4954,19 @@
           <t>energy_cost_RMSE</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="n">
+        <v>0.2952</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -4970,17 +4974,19 @@
           <t>environmental_MAE</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="n">
+        <v>0.263</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -4988,17 +4994,19 @@
           <t>environmental_RMSE</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="n">
+        <v>0.323</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5006,17 +5014,19 @@
           <t>comfort_MAE</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="n">
+        <v>0.1829</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5024,17 +5034,19 @@
           <t>comfort_RMSE</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="n">
+        <v>0.2341</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5042,17 +5054,19 @@
           <t>practicality_MAE</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="n">
+        <v>0.1967</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5060,17 +5074,19 @@
           <t>practicality_RMSE</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="n">
+        <v>0.2539</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5078,17 +5094,19 @@
           <t>overall_MAE</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="n">
+        <v>0.2215</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5096,17 +5114,19 @@
           <t>overall_RMSE</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="n">
+        <v>0.2787</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5115,18 +5135,18 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1</v>
+        <v>-0.0017</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5135,18 +5155,18 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1</v>
+        <v>0.0051</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -5155,18 +5175,18 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1</v>
+        <v>0.3179</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -5175,18 +5195,18 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -5195,18 +5215,18 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -5214,17 +5234,19 @@
           <t>energy_cost_MAE</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="n">
+        <v>0.2335</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -5232,17 +5254,19 @@
           <t>energy_cost_RMSE</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="n">
+        <v>0.2757</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -5250,17 +5274,19 @@
           <t>environmental_MAE</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="n">
+        <v>0.2327</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -5268,17 +5294,19 @@
           <t>environmental_RMSE</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="n">
+        <v>0.2742</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -5286,17 +5314,19 @@
           <t>comfort_MAE</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="n">
+        <v>0.1975</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -5304,17 +5334,19 @@
           <t>comfort_RMSE</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="n">
+        <v>0.2466</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -5322,17 +5354,19 @@
           <t>practicality_MAE</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="n">
+        <v>0.121</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -5340,17 +5374,19 @@
           <t>practicality_RMSE</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="n">
+        <v>0.1591</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -5358,17 +5394,19 @@
           <t>overall_MAE</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="n">
+        <v>0.1962</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -5376,17 +5414,19 @@
           <t>overall_RMSE</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="n">
+        <v>0.2436</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -5395,18 +5435,18 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>0.8689</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -5415,18 +5455,18 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>0.8815</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -5435,18 +5475,18 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -5455,18 +5495,18 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>0.9833</v>
+        <v>0.6714</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -5475,7 +5515,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="272">
@@ -5486,7 +5526,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -5495,7 +5535,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>0.2434</v>
+        <v>0.3034</v>
       </c>
     </row>
     <row r="273">
@@ -5506,7 +5546,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -5515,7 +5555,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>0.2952</v>
+        <v>0.3541</v>
       </c>
     </row>
     <row r="274">
@@ -5526,7 +5566,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -5535,7 +5575,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>0.263</v>
+        <v>0.3679</v>
       </c>
     </row>
     <row r="275">
@@ -5546,7 +5586,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -5555,7 +5595,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>0.323</v>
+        <v>0.4246</v>
       </c>
     </row>
     <row r="276">
@@ -5566,7 +5606,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -5575,7 +5615,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>0.1829</v>
+        <v>0.1893</v>
       </c>
     </row>
     <row r="277">
@@ -5586,7 +5626,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -5595,7 +5635,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>0.2341</v>
+        <v>0.2383</v>
       </c>
     </row>
     <row r="278">
@@ -5606,7 +5646,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -5615,7 +5655,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>0.1967</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="279">
@@ -5626,7 +5666,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -5635,7 +5675,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>0.2539</v>
+        <v>0.2885</v>
       </c>
     </row>
     <row r="280">
@@ -5646,7 +5686,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -5655,7 +5695,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>0.2215</v>
+        <v>0.2751</v>
       </c>
     </row>
     <row r="281">
@@ -5666,7 +5706,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -5675,7 +5715,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>0.2787</v>
+        <v>0.3338</v>
       </c>
     </row>
     <row r="282">
@@ -5686,7 +5726,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -5695,7 +5735,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>-0.0017</v>
+        <v>-0.1282</v>
       </c>
     </row>
     <row r="283">
@@ -5706,7 +5746,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -5715,7 +5755,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>0.0051</v>
+        <v>-0.1231</v>
       </c>
     </row>
     <row r="284">
@@ -5726,7 +5766,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -5735,7 +5775,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>0.3179</v>
+        <v>0.2154</v>
       </c>
     </row>
     <row r="285">
@@ -5746,7 +5786,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -5755,7 +5795,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>0.641</v>
+        <v>0.5846</v>
       </c>
     </row>
     <row r="286">
@@ -5766,7 +5806,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -5775,7 +5815,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>195</v>
+        <v>65</v>
       </c>
     </row>
     <row r="287">
@@ -5786,7 +5826,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -5795,7 +5835,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>0.2335</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="288">
@@ -5806,7 +5846,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -5815,7 +5855,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>0.2757</v>
+        <v>0.2423</v>
       </c>
     </row>
     <row r="289">
@@ -5826,7 +5866,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -5835,7 +5875,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>0.2327</v>
+        <v>0.1849</v>
       </c>
     </row>
     <row r="290">
@@ -5846,7 +5886,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -5855,7 +5895,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>0.2742</v>
+        <v>0.2365</v>
       </c>
     </row>
     <row r="291">
@@ -5866,7 +5906,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -5875,7 +5915,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0.1975</v>
+        <v>0.1591</v>
       </c>
     </row>
     <row r="292">
@@ -5886,7 +5926,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -5895,7 +5935,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0.2466</v>
+        <v>0.2137</v>
       </c>
     </row>
     <row r="293">
@@ -5906,7 +5946,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -5915,7 +5955,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0.121</v>
+        <v>0.2382</v>
       </c>
     </row>
     <row r="294">
@@ -5926,7 +5966,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -5935,7 +5975,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>0.1591</v>
+        <v>0.2996</v>
       </c>
     </row>
     <row r="295">
@@ -5946,7 +5986,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -5955,7 +5995,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0.1962</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="296">
@@ -5966,7 +6006,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -5975,7 +6015,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0.2436</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="297">
@@ -5986,7 +6026,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -5995,7 +6035,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>0.0571</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="298">
@@ -6006,7 +6046,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6015,7 +6055,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0.0429</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="299">
@@ -6026,7 +6066,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6035,7 +6075,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>0.4</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="300">
@@ -6046,7 +6086,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -6055,7 +6095,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>0.6714</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="301">
@@ -6066,7 +6106,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -6075,18 +6115,18 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -6095,18 +6135,18 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0.3034</v>
+        <v>0.1705</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -6115,18 +6155,18 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>0.3541</v>
+        <v>0.2303</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -6135,18 +6175,18 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>0.3679</v>
+        <v>0.1687</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -6155,18 +6195,18 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>0.4246</v>
+        <v>0.2312</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -6175,18 +6215,18 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>0.1893</v>
+        <v>0.1573</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -6195,18 +6235,18 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>0.2383</v>
+        <v>0.2229</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -6215,18 +6255,18 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>0.24</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -6235,18 +6275,18 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>0.2885</v>
+        <v>0.1979</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -6255,18 +6295,18 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>0.2751</v>
+        <v>0.1589</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -6275,18 +6315,18 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>0.3338</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -6295,18 +6335,18 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>-0.1282</v>
+        <v>0.2821</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -6315,18 +6355,18 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>-0.1231</v>
+        <v>0.3231</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -6335,18 +6375,18 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>0.2154</v>
+        <v>0.5128</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -6355,18 +6395,18 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>0.5846</v>
+        <v>0.7949000000000001</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -6375,18 +6415,18 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -6395,18 +6435,18 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>0.1899</v>
+        <v>0.2002</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -6415,18 +6455,18 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>0.2423</v>
+        <v>0.2581</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -6435,18 +6475,18 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>0.1849</v>
+        <v>0.1998</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -6455,18 +6495,18 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>0.2365</v>
+        <v>0.2563</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -6475,18 +6515,18 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>0.1591</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -6495,18 +6535,18 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>0.2137</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -6515,18 +6555,18 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>0.2382</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -6535,18 +6575,18 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>0.2996</v>
+        <v>0.1329</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -6555,18 +6595,18 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>0.193</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -6575,18 +6615,18 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>0.25</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -6595,18 +6635,18 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>0.0667</v>
+        <v>0.1905</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -6615,18 +6655,18 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>0.1</v>
+        <v>0.2357</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -6635,18 +6675,18 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0.3333</v>
+        <v>0.4429</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -6655,18 +6695,18 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>0.6667</v>
+        <v>0.7286</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -6675,7 +6715,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="332">
@@ -6686,7 +6726,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -6695,7 +6735,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>0.1705</v>
+        <v>0.1546</v>
       </c>
     </row>
     <row r="333">
@@ -6706,7 +6746,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -6715,7 +6755,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>0.2303</v>
+        <v>0.2137</v>
       </c>
     </row>
     <row r="334">
@@ -6726,7 +6766,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -6735,7 +6775,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>0.1687</v>
+        <v>0.1514</v>
       </c>
     </row>
     <row r="335">
@@ -6746,7 +6786,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -6755,7 +6795,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>0.2312</v>
+        <v>0.2182</v>
       </c>
     </row>
     <row r="336">
@@ -6766,7 +6806,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -6775,7 +6815,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>0.1573</v>
+        <v>0.2098</v>
       </c>
     </row>
     <row r="337">
@@ -6786,7 +6826,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -6795,7 +6835,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>0.2229</v>
+        <v>0.2655</v>
       </c>
     </row>
     <row r="338">
@@ -6806,7 +6846,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -6815,7 +6855,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>0.139</v>
+        <v>0.1988</v>
       </c>
     </row>
     <row r="339">
@@ -6826,7 +6866,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -6835,7 +6875,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>0.1979</v>
+        <v>0.2606</v>
       </c>
     </row>
     <row r="340">
@@ -6846,7 +6886,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -6855,7 +6895,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>0.1589</v>
+        <v>0.1786</v>
       </c>
     </row>
     <row r="341">
@@ -6866,7 +6906,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -6875,7 +6915,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>0.221</v>
+        <v>0.2407</v>
       </c>
     </row>
     <row r="342">
@@ -6886,7 +6926,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -6895,7 +6935,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>0.2821</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="343">
@@ -6906,7 +6946,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -6915,7 +6955,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>0.3231</v>
+        <v>0.2769</v>
       </c>
     </row>
     <row r="344">
@@ -6926,7 +6966,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -6935,7 +6975,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>0.5128</v>
+        <v>0.5077</v>
       </c>
     </row>
     <row r="345">
@@ -6946,7 +6986,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -6955,7 +6995,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.8308</v>
       </c>
     </row>
     <row r="346">
@@ -6966,7 +7006,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -6975,7 +7015,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>195</v>
+        <v>65</v>
       </c>
     </row>
     <row r="347">
@@ -6986,7 +7026,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -6995,7 +7035,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>0.2002</v>
+        <v>0.1529</v>
       </c>
     </row>
     <row r="348">
@@ -7006,7 +7046,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -7015,7 +7055,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>0.2581</v>
+        <v>0.2126</v>
       </c>
     </row>
     <row r="349">
@@ -7026,7 +7066,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -7035,7 +7075,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>0.1998</v>
+        <v>0.1513</v>
       </c>
     </row>
     <row r="350">
@@ -7046,7 +7086,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -7055,7 +7095,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>0.2563</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="351">
@@ -7066,7 +7106,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -7075,7 +7115,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>0.143</v>
+        <v>0.1172</v>
       </c>
     </row>
     <row r="352">
@@ -7086,7 +7126,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -7095,7 +7135,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>0.196</v>
+        <v>0.2006</v>
       </c>
     </row>
     <row r="353">
@@ -7106,7 +7146,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -7115,7 +7155,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1327</v>
       </c>
     </row>
     <row r="354">
@@ -7126,7 +7166,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -7135,7 +7175,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>0.1329</v>
+        <v>0.1818</v>
       </c>
     </row>
     <row r="355">
@@ -7146,7 +7186,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -7155,7 +7195,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>0.158</v>
+        <v>0.1385</v>
       </c>
     </row>
     <row r="356">
@@ -7166,7 +7206,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -7175,7 +7215,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>0.217</v>
+        <v>0.2025</v>
       </c>
     </row>
     <row r="357">
@@ -7186,7 +7226,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -7195,7 +7235,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>0.1905</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="358">
@@ -7206,7 +7246,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -7215,7 +7255,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>0.2357</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="359">
@@ -7226,7 +7266,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -7235,7 +7275,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>0.4429</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="360">
@@ -7246,7 +7286,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -7255,7 +7295,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0.7286</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="361">
@@ -7266,7 +7306,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -7275,18 +7315,18 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -7295,18 +7335,18 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>0.1546</v>
+        <v>0.1045</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -7315,18 +7355,18 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>0.2137</v>
+        <v>0.1759</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -7335,18 +7375,18 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>0.1514</v>
+        <v>0.1413</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -7355,18 +7395,18 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>0.2182</v>
+        <v>0.2412</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -7375,18 +7415,18 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>0.2098</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -7395,18 +7435,18 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>0.2655</v>
+        <v>0.0356</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -7415,18 +7455,18 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>0.1988</v>
+        <v>0.0164</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -7435,18 +7475,18 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>0.2606</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -7455,18 +7495,18 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>0.1786</v>
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -7475,18 +7515,18 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>0.2407</v>
+        <v>0.1525</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -7495,18 +7535,18 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>0.241</v>
+        <v>0.8769</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -7515,18 +7555,18 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>0.2769</v>
+        <v>0.8872</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -7535,18 +7575,18 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>0.5077</v>
+        <v>0.9026</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -7555,18 +7595,18 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>0.8308</v>
+        <v>0.9641</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -7575,18 +7615,18 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -7595,18 +7635,18 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>0.1529</v>
+        <v>0.08749999999999999</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -7615,18 +7655,18 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>0.2126</v>
+        <v>0.1311</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -7635,18 +7675,18 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>0.1513</v>
+        <v>0.0842</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -7655,18 +7695,18 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>0.2132</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -7675,18 +7715,18 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>0.1172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -7695,18 +7735,18 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>0.2006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -7715,18 +7755,18 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>0.1327</v>
+        <v>0.0237</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -7735,18 +7775,18 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>0.1818</v>
+        <v>0.0305</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -7755,18 +7795,18 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>0.1385</v>
+        <v>0.0488</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -7775,18 +7815,18 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>0.2025</v>
+        <v>0.0915</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -7795,18 +7835,18 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>0.4333</v>
+        <v>0.8762</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -7815,18 +7855,18 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>0.475</v>
+        <v>0.8929</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -7835,18 +7875,18 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>0.6</v>
+        <v>0.8571</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -7855,18 +7895,18 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>0.8333</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -7875,7 +7915,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="392">
@@ -7886,7 +7926,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -7895,7 +7935,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>0.1045</v>
+        <v>0.1727</v>
       </c>
     </row>
     <row r="393">
@@ -7906,7 +7946,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -7915,7 +7955,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>0.1759</v>
+        <v>0.2551</v>
       </c>
     </row>
     <row r="394">
@@ -7926,7 +7966,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -7935,7 +7975,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>0.1413</v>
+        <v>0.2879</v>
       </c>
     </row>
     <row r="395">
@@ -7946,7 +7986,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -7955,7 +7995,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>0.2412</v>
+        <v>0.3861</v>
       </c>
     </row>
     <row r="396">
@@ -7966,7 +8006,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -7975,7 +8015,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="397">
@@ -7986,7 +8026,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -7995,7 +8035,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>0.0356</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="398">
@@ -8006,7 +8046,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -8015,7 +8055,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>0.0164</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="399">
@@ -8026,7 +8066,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -8035,7 +8075,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>0.0507</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="400">
@@ -8046,7 +8086,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -8055,7 +8095,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.1153</v>
       </c>
     </row>
     <row r="401">
@@ -8066,7 +8106,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -8075,7 +8115,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>0.1525</v>
+        <v>0.2314</v>
       </c>
     </row>
     <row r="402">
@@ -8086,7 +8126,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -8095,7 +8135,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>0.8769</v>
+        <v>0.8974</v>
       </c>
     </row>
     <row r="403">
@@ -8106,7 +8146,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -8115,7 +8155,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>0.8872</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="404">
@@ -8126,7 +8166,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -8135,7 +8175,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>0.9026</v>
+        <v>0.9385</v>
       </c>
     </row>
     <row r="405">
@@ -8146,7 +8186,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -8155,7 +8195,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>0.9641</v>
+        <v>0.9692</v>
       </c>
     </row>
     <row r="406">
@@ -8166,7 +8206,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -8175,7 +8215,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>195</v>
+        <v>65</v>
       </c>
     </row>
     <row r="407">
@@ -8186,7 +8226,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -8195,7 +8235,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0503</v>
       </c>
     </row>
     <row r="408">
@@ -8206,7 +8246,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -8215,7 +8255,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>0.1311</v>
+        <v>0.1003</v>
       </c>
     </row>
     <row r="409">
@@ -8226,7 +8266,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -8235,7 +8275,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>0.0842</v>
+        <v>0.0493</v>
       </c>
     </row>
     <row r="410">
@@ -8246,7 +8286,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -8255,7 +8295,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>0.124</v>
+        <v>0.0982</v>
       </c>
     </row>
     <row r="411">
@@ -8266,7 +8306,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -8275,7 +8315,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>0</v>
+        <v>0.0271</v>
       </c>
     </row>
     <row r="412">
@@ -8286,7 +8326,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -8295,7 +8335,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>0</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="413">
@@ -8306,7 +8346,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -8315,7 +8355,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>0.0237</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="414">
@@ -8326,7 +8366,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -8335,7 +8375,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>0.0305</v>
+        <v>0.0851</v>
       </c>
     </row>
     <row r="415">
@@ -8346,7 +8386,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -8355,7 +8395,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>0.0488</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="416">
@@ -8366,7 +8406,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -8375,7 +8415,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>0.0915</v>
+        <v>0.0881</v>
       </c>
     </row>
     <row r="417">
@@ -8386,7 +8426,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -8395,7 +8435,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>0.8762</v>
+        <v>0.8556</v>
       </c>
     </row>
     <row r="418">
@@ -8406,7 +8446,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -8415,7 +8455,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>0.8929</v>
+        <v>0.8667</v>
       </c>
     </row>
     <row r="419">
@@ -8426,7 +8466,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -8435,7 +8475,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>0.8571</v>
+        <v>0.9167</v>
       </c>
     </row>
     <row r="420">
@@ -8446,7 +8486,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -8455,7 +8495,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>0.9714</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="421">
@@ -8466,7 +8506,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -8475,613 +8515,613 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>match_content</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>0.1727</v>
+        <v>195</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>match_no_match</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>0.2551</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>n_failed_scenarios</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>0.2879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>n_total_arch_scenarios</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>0.3861</v>
+        <v>195</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>total_failure_rate</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>cross_criterion_rho_overall</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>0.0014</v>
+        <v>0.9202</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>cross_criterion_rho_pvalue</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>cross_criterion_rho_HVAC</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>0.002</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>cross_criterion_rho_HVAC_pvalue</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>0.1153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>cross_criterion_rho_Appliance</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>0.2314</v>
+        <v>0.8988</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>cross_criterion_rho_Appliance_pvalue</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>0.8974</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>cross_criterion_rho_Shower</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>0.9</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>cross_criterion_rho_Shower_pvalue</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>0.9385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>match_content</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>0.9692</v>
+        <v>195</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>match_no_match</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>energy_cost_MAE</t>
+          <t>n_failed_scenarios</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>0.0503</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>energy_cost_RMSE</t>
+          <t>n_total_arch_scenarios</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>0.1003</v>
+        <v>195</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>environmental_MAE</t>
+          <t>total_failure_rate</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>0.0493</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>environmental_RMSE</t>
+          <t>cross_criterion_rho_overall</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>0.0982</v>
+        <v>0.9202</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>comfort_MAE</t>
+          <t>cross_criterion_rho_pvalue</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>0.0271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>comfort_RMSE</t>
+          <t>cross_criterion_rho_HVAC</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>practicality_MAE</t>
+          <t>cross_criterion_rho_HVAC_pvalue</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>0.0252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>practicality_RMSE</t>
+          <t>cross_criterion_rho_Appliance</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>0.0851</v>
+        <v>0.8988</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>overall_MAE</t>
+          <t>cross_criterion_rho_Appliance_pvalue</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>overall_RMSE</t>
+          <t>cross_criterion_rho_Shower</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>0.0881</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>cross_criterion_rho_Shower_pvalue</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>0.8556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>match_content</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>0.8667</v>
+        <v>195</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>match_no_match</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>0.9167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>n_failed_scenarios</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>n_scenarios_evaluated</t>
+          <t>n_total_arch_scenarios</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>60</v>
+        <v>195</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -9091,17 +9131,17 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>match_content</t>
+          <t>total_failure_rate</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -9111,17 +9151,17 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>match_no_match</t>
+          <t>cross_criterion_rho_overall</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>0</v>
+        <v>0.9202</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -9131,7 +9171,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>n_failed_scenarios</t>
+          <t>cross_criterion_rho_pvalue</t>
         </is>
       </c>
       <c r="D454" t="n">
@@ -9141,7 +9181,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -9151,17 +9191,17 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>n_total_arch_scenarios</t>
+          <t>cross_criterion_rho_HVAC</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>195</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -9171,7 +9211,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>total_failure_rate</t>
+          <t>cross_criterion_rho_HVAC_pvalue</t>
         </is>
       </c>
       <c r="D456" t="n">
@@ -9181,7 +9221,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -9191,17 +9231,17 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_overall</t>
+          <t>cross_criterion_rho_Appliance</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>0.9202</v>
+        <v>0.8988</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -9211,7 +9251,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_pvalue</t>
+          <t>cross_criterion_rho_Appliance_pvalue</t>
         </is>
       </c>
       <c r="D458" t="n">
@@ -9221,7 +9261,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -9231,17 +9271,17 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_HVAC</t>
+          <t>cross_criterion_rho_Shower</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>0.9992</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>FixedDefault</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -9251,7 +9291,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_HVAC_pvalue</t>
+          <t>cross_criterion_rho_Shower_pvalue</t>
         </is>
       </c>
       <c r="D460" t="n">
@@ -9261,7 +9301,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -9271,17 +9311,17 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Appliance</t>
+          <t>match_content</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>0.8988</v>
+        <v>195</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -9291,7 +9331,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Appliance_pvalue</t>
+          <t>match_no_match</t>
         </is>
       </c>
       <c r="D462" t="n">
@@ -9301,7 +9341,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -9311,17 +9351,17 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Shower</t>
+          <t>n_failed_scenarios</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>0.9661999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -9331,17 +9371,17 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Shower_pvalue</t>
+          <t>n_total_arch_scenarios</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -9351,17 +9391,17 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>match_content</t>
+          <t>total_failure_rate</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -9371,17 +9411,17 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>match_no_match</t>
+          <t>cross_criterion_rho_overall</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>0</v>
+        <v>0.9202</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -9391,7 +9431,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>n_failed_scenarios</t>
+          <t>cross_criterion_rho_pvalue</t>
         </is>
       </c>
       <c r="D467" t="n">
@@ -9401,7 +9441,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -9411,17 +9451,17 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>n_total_arch_scenarios</t>
+          <t>cross_criterion_rho_HVAC</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>195</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -9431,7 +9471,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>total_failure_rate</t>
+          <t>cross_criterion_rho_HVAC_pvalue</t>
         </is>
       </c>
       <c r="D469" t="n">
@@ -9441,7 +9481,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -9451,17 +9491,17 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_overall</t>
+          <t>cross_criterion_rho_Appliance</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>0.9202</v>
+        <v>0.8988</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -9471,7 +9511,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_pvalue</t>
+          <t>cross_criterion_rho_Appliance_pvalue</t>
         </is>
       </c>
       <c r="D471" t="n">
@@ -9481,7 +9521,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -9491,17 +9531,17 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_HVAC</t>
+          <t>cross_criterion_rho_Shower</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>0.9992</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>NearestNeighbor</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -9511,7 +9551,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_HVAC_pvalue</t>
+          <t>cross_criterion_rho_Shower_pvalue</t>
         </is>
       </c>
       <c r="D473" t="n">
@@ -9521,7 +9561,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -9531,17 +9571,17 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Appliance</t>
+          <t>match_content</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>0.8988</v>
+        <v>195</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -9551,7 +9591,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Appliance_pvalue</t>
+          <t>match_no_match</t>
         </is>
       </c>
       <c r="D475" t="n">
@@ -9561,7 +9601,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -9571,17 +9611,17 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Shower</t>
+          <t>diag_files_loaded</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>0.9661999999999999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Uniform</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -9591,17 +9631,17 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Shower_pvalue</t>
+          <t>diag_total_scenarios</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -9611,17 +9651,17 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>match_content</t>
+          <t>diag_failed_scenarios</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -9631,17 +9671,17 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>match_no_match</t>
+          <t>diag_successful_scenarios</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>0</v>
+        <v>973</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -9651,17 +9691,17 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>n_failed_scenarios</t>
+          <t>diag_failed_calls</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -9671,17 +9711,17 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>n_total_arch_scenarios</t>
+          <t>diag_successful_calls</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>70</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -9691,17 +9731,17 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>total_failure_rate</t>
+          <t>diag_EXTRACTION_INVALID_JSON</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -9711,17 +9751,17 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_overall</t>
+          <t>diag_FAILED_MISSING_SCORE</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>0.9992</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -9731,7 +9771,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_pvalue</t>
+          <t>diag_FAILED_OUT_OF_BOUNDS</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -9741,7 +9781,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -9751,17 +9791,17 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_HVAC</t>
+          <t>diag_FAILED_INVALID_SCORE_TYPE</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>0.9992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -9771,7 +9811,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_HVAC_pvalue</t>
+          <t>diag_FAILED_API_EXHAUSTED</t>
         </is>
       </c>
       <c r="D486" t="n">
@@ -9781,7 +9821,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -9791,15 +9831,17 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Appliance</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr"/>
+          <t>diag_FAILED_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -9809,15 +9851,17 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Appliance_pvalue</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr"/>
+          <t>n_runs</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -9827,15 +9871,17 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Shower</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr"/>
+          <t>n_successful_runs_mean</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>4.99</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>FixedDefault</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -9845,15 +9891,17 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Shower_pvalue</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr"/>
+          <t>n_failed_scenarios</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -9863,7 +9911,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>match_content</t>
+          <t>n_total_arch_scenarios</t>
         </is>
       </c>
       <c r="D491" t="n">
@@ -9873,7 +9921,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -9883,7 +9931,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>match_no_match</t>
+          <t>total_failure_rate</t>
         </is>
       </c>
       <c r="D492" t="n">
@@ -9893,7 +9941,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -9903,17 +9951,17 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>n_failed_scenarios</t>
+          <t>cross_criterion_rho_overall</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>0</v>
+        <v>0.9202</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -9923,17 +9971,17 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>n_total_arch_scenarios</t>
+          <t>cross_criterion_rho_pvalue</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -9943,17 +9991,17 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>total_failure_rate</t>
+          <t>cross_criterion_rho_HVAC</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>0</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -9963,17 +10011,17 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_overall</t>
+          <t>cross_criterion_rho_HVAC_pvalue</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>0.9202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -9983,17 +10031,17 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_pvalue</t>
+          <t>cross_criterion_rho_Appliance</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>0</v>
+        <v>0.8988</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -10003,17 +10051,17 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_HVAC</t>
+          <t>cross_criterion_rho_Appliance_pvalue</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>0.9992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -10023,17 +10071,17 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_HVAC_pvalue</t>
+          <t>cross_criterion_rho_Shower</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>0</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -10043,17 +10091,17 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Appliance</t>
+          <t>cross_criterion_rho_Shower_pvalue</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>0.8988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -10063,17 +10111,17 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Appliance_pvalue</t>
+          <t>match_content</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -10083,17 +10131,17 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Shower</t>
+          <t>match_no_match</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>0.9661999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>NearestNeighbor</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -10103,17 +10151,17 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Shower_pvalue</t>
+          <t>diag_files_loaded</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -10123,17 +10171,17 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>match_content</t>
+          <t>diag_total_scenarios</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>195</v>
+        <v>975</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -10143,7 +10191,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>match_no_match</t>
+          <t>diag_failed_scenarios</t>
         </is>
       </c>
       <c r="D505" t="n">
@@ -10153,7 +10201,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -10163,17 +10211,17 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>n_failed_scenarios</t>
+          <t>diag_successful_scenarios</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -10183,17 +10231,17 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>n_total_arch_scenarios</t>
+          <t>diag_failed_calls</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -10203,17 +10251,17 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>total_failure_rate</t>
+          <t>diag_successful_calls</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>0</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -10223,17 +10271,17 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_overall</t>
+          <t>diag_EXTRACTION_INVALID_JSON</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>0.9199000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -10243,7 +10291,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_pvalue</t>
+          <t>diag_FAILED_MISSING_SCORE</t>
         </is>
       </c>
       <c r="D510" t="n">
@@ -10253,7 +10301,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -10263,17 +10311,17 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_HVAC</t>
+          <t>diag_FAILED_OUT_OF_BOUNDS</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>0.9992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -10283,7 +10331,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_HVAC_pvalue</t>
+          <t>diag_FAILED_INVALID_SCORE_TYPE</t>
         </is>
       </c>
       <c r="D512" t="n">
@@ -10293,7 +10341,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -10303,17 +10351,17 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Appliance</t>
+          <t>diag_FAILED_API_EXHAUSTED</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>0.8988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -10323,7 +10371,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Appliance_pvalue</t>
+          <t>diag_FAILED_UNKNOWN</t>
         </is>
       </c>
       <c r="D514" t="n">
@@ -10333,7 +10381,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -10343,17 +10391,17 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Shower</t>
+          <t>n_runs</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>0.9659</v>
+        <v>5</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -10363,17 +10411,17 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Shower_pvalue</t>
+          <t>n_successful_runs_mean</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -10383,17 +10431,17 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>match_content</t>
+          <t>n_failed_scenarios</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -10403,17 +10451,17 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>match_no_match</t>
+          <t>n_total_arch_scenarios</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -10423,17 +10471,17 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>diag_files_loaded</t>
+          <t>total_failure_rate</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -10443,17 +10491,17 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>diag_total_scenarios</t>
+          <t>cross_criterion_rho_overall</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>975</v>
+        <v>0.9202</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -10463,17 +10511,17 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>diag_failed_scenarios</t>
+          <t>cross_criterion_rho_pvalue</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -10483,17 +10531,17 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>diag_successful_scenarios</t>
+          <t>cross_criterion_rho_HVAC</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>973</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -10503,17 +10551,17 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>diag_failed_calls</t>
+          <t>cross_criterion_rho_HVAC_pvalue</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -10523,17 +10571,17 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>diag_successful_calls</t>
+          <t>cross_criterion_rho_Appliance</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>2923</v>
+        <v>0.8988</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -10543,17 +10591,17 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>diag_EXTRACTION_INVALID_JSON</t>
+          <t>cross_criterion_rho_Appliance_pvalue</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -10563,17 +10611,17 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>diag_FAILED_MISSING_SCORE</t>
+          <t>cross_criterion_rho_Shower</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>1</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -10583,7 +10631,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>diag_FAILED_OUT_OF_BOUNDS</t>
+          <t>cross_criterion_rho_Shower_pvalue</t>
         </is>
       </c>
       <c r="D527" t="n">
@@ -10593,7 +10641,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -10603,17 +10651,17 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>diag_FAILED_INVALID_SCORE_TYPE</t>
+          <t>match_content</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -10623,7 +10671,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>diag_FAILED_API_EXHAUSTED</t>
+          <t>match_no_match</t>
         </is>
       </c>
       <c r="D529" t="n">
@@ -10633,7 +10681,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -10643,17 +10691,17 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>diag_FAILED_UNKNOWN</t>
+          <t>diag_files_loaded</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -10663,17 +10711,17 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>n_runs</t>
+          <t>diag_total_scenarios</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>5</v>
+        <v>975</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -10683,17 +10731,17 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>n_successful_runs_mean</t>
+          <t>diag_failed_scenarios</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>4.99</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -10703,17 +10751,17 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>n_failed_scenarios</t>
+          <t>diag_successful_scenarios</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>0</v>
+        <v>973</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -10723,17 +10771,17 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>n_total_arch_scenarios</t>
+          <t>diag_failed_calls</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>195</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -10743,17 +10791,17 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>total_failure_rate</t>
+          <t>diag_successful_calls</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>0</v>
+        <v>973</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -10763,17 +10811,17 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_overall</t>
+          <t>diag_FAILED_EXTRACTION_NON_JSON_WRAPPER</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>0.9202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -10783,7 +10831,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_pvalue</t>
+          <t>diag_EXTRACTION_INVALID_JSON</t>
         </is>
       </c>
       <c r="D537" t="n">
@@ -10793,7 +10841,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -10803,17 +10851,17 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_HVAC</t>
+          <t>diag_FAILED_EXTRACTION_INVALID_DECISION_TYPE</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>0.9992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -10823,7 +10871,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_HVAC_pvalue</t>
+          <t>diag_FAILED_EXTRACTION_INVALID_CALCULATOR</t>
         </is>
       </c>
       <c r="D539" t="n">
@@ -10833,7 +10881,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -10843,17 +10891,17 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Appliance</t>
+          <t>diag_FAILED_EXTRACTION_MISSING_PARAMETERS</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>0.8988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -10863,7 +10911,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Appliance_pvalue</t>
+          <t>diag_FAILED_EXTRACTION_EXCEPTION</t>
         </is>
       </c>
       <c r="D541" t="n">
@@ -10873,7 +10921,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -10883,17 +10931,17 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Shower</t>
+          <t>diag_FAILED_GROUND_TRUTH_CALCULATION_EXCEPTION</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>0.9661999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -10903,7 +10951,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>cross_criterion_rho_Shower_pvalue</t>
+          <t>diag_FAILED_GROUND_TRUTH_MISSING_KEY</t>
         </is>
       </c>
       <c r="D543" t="n">
@@ -10913,7 +10961,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -10923,17 +10971,17 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>match_content</t>
+          <t>diag_FAILED_API_EXHAUSTED</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -10943,7 +10991,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>match_no_match</t>
+          <t>diag_FAILED_UNKNOWN</t>
         </is>
       </c>
       <c r="D545" t="n">
@@ -10953,7 +11001,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -10963,7 +11011,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>diag_files_loaded</t>
+          <t>n_runs</t>
         </is>
       </c>
       <c r="D546" t="n">
@@ -10973,7 +11021,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -10983,17 +11031,17 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>diag_total_scenarios</t>
+          <t>n_successful_runs_mean</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>975</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -11003,7 +11051,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>diag_failed_scenarios</t>
+          <t>n_failed_scenarios</t>
         </is>
       </c>
       <c r="D548" t="n">
@@ -11013,7 +11061,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -11023,17 +11071,17 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>diag_successful_scenarios</t>
+          <t>n_total_arch_scenarios</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>975</v>
+        <v>195</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -11043,7 +11091,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>diag_failed_calls</t>
+          <t>total_failure_rate</t>
         </is>
       </c>
       <c r="D550" t="n">
@@ -11053,7 +11101,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -11063,17 +11111,17 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>diag_successful_calls</t>
+          <t>extraction_failure_rate</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>2925</v>
+        <v>0.0051</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -11083,7 +11131,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>diag_EXTRACTION_INVALID_JSON</t>
+          <t>calculation_failure_rate</t>
         </is>
       </c>
       <c r="D552" t="n">
@@ -11093,7 +11141,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -11103,17 +11151,17 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>diag_FAILED_MISSING_SCORE</t>
+          <t>n_extraction_failures</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -11123,7 +11171,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>diag_FAILED_OUT_OF_BOUNDS</t>
+          <t>n_calculation_failures</t>
         </is>
       </c>
       <c r="D554" t="n">
@@ -11133,7 +11181,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -11143,17 +11191,17 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>diag_FAILED_INVALID_SCORE_TYPE</t>
+          <t>cross_criterion_rho_overall</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>0</v>
+        <v>0.9202</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -11163,7 +11211,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>diag_FAILED_API_EXHAUSTED</t>
+          <t>cross_criterion_rho_pvalue</t>
         </is>
       </c>
       <c r="D556" t="n">
@@ -11173,7 +11221,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -11183,17 +11231,17 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>diag_FAILED_UNKNOWN</t>
+          <t>cross_criterion_rho_HVAC</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>0</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -11203,17 +11251,17 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>n_runs</t>
+          <t>cross_criterion_rho_HVAC_pvalue</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -11223,17 +11271,17 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>n_successful_runs_mean</t>
+          <t>cross_criterion_rho_Appliance</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>5</v>
+        <v>0.8988</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -11243,7 +11291,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>n_failed_scenarios</t>
+          <t>cross_criterion_rho_Appliance_pvalue</t>
         </is>
       </c>
       <c r="D560" t="n">
@@ -11253,7 +11301,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -11263,17 +11311,17 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>n_total_arch_scenarios</t>
+          <t>cross_criterion_rho_Shower</t>
         </is>
       </c>
       <c r="D561" t="n">
-        <v>195</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -11283,870 +11331,10 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>total_failure_rate</t>
+          <t>cross_criterion_rho_Shower_pvalue</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_overall</t>
-        </is>
-      </c>
-      <c r="D563" t="n">
-        <v>0.9202</v>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_pvalue</t>
-        </is>
-      </c>
-      <c r="D564" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_HVAC</t>
-        </is>
-      </c>
-      <c r="D565" t="n">
-        <v>0.9992</v>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_HVAC_pvalue</t>
-        </is>
-      </c>
-      <c r="D566" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_Appliance</t>
-        </is>
-      </c>
-      <c r="D567" t="n">
-        <v>0.8988</v>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_Appliance_pvalue</t>
-        </is>
-      </c>
-      <c r="D568" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_Shower</t>
-        </is>
-      </c>
-      <c r="D569" t="n">
-        <v>0.9661999999999999</v>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_Shower_pvalue</t>
-        </is>
-      </c>
-      <c r="D570" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C571" t="inlineStr">
-        <is>
-          <t>match_content</t>
-        </is>
-      </c>
-      <c r="D571" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C572" t="inlineStr">
-        <is>
-          <t>match_no_match</t>
-        </is>
-      </c>
-      <c r="D572" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C573" t="inlineStr">
-        <is>
-          <t>diag_files_loaded</t>
-        </is>
-      </c>
-      <c r="D573" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B574" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C574" t="inlineStr">
-        <is>
-          <t>diag_total_scenarios</t>
-        </is>
-      </c>
-      <c r="D574" t="n">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C575" t="inlineStr">
-        <is>
-          <t>diag_failed_scenarios</t>
-        </is>
-      </c>
-      <c r="D575" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B576" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C576" t="inlineStr">
-        <is>
-          <t>diag_successful_scenarios</t>
-        </is>
-      </c>
-      <c r="D576" t="n">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C577" t="inlineStr">
-        <is>
-          <t>diag_failed_calls</t>
-        </is>
-      </c>
-      <c r="D577" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C578" t="inlineStr">
-        <is>
-          <t>diag_successful_calls</t>
-        </is>
-      </c>
-      <c r="D578" t="n">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t>diag_FAILED_EXTRACTION_NON_JSON_WRAPPER</t>
-        </is>
-      </c>
-      <c r="D579" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B580" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C580" t="inlineStr">
-        <is>
-          <t>diag_EXTRACTION_INVALID_JSON</t>
-        </is>
-      </c>
-      <c r="D580" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B581" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C581" t="inlineStr">
-        <is>
-          <t>diag_FAILED_EXTRACTION_INVALID_DECISION_TYPE</t>
-        </is>
-      </c>
-      <c r="D581" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C582" t="inlineStr">
-        <is>
-          <t>diag_FAILED_EXTRACTION_INVALID_CALCULATOR</t>
-        </is>
-      </c>
-      <c r="D582" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C583" t="inlineStr">
-        <is>
-          <t>diag_FAILED_EXTRACTION_MISSING_PARAMETERS</t>
-        </is>
-      </c>
-      <c r="D583" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B584" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C584" t="inlineStr">
-        <is>
-          <t>diag_FAILED_EXTRACTION_EXCEPTION</t>
-        </is>
-      </c>
-      <c r="D584" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B585" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C585" t="inlineStr">
-        <is>
-          <t>diag_FAILED_GROUND_TRUTH_CALCULATION_EXCEPTION</t>
-        </is>
-      </c>
-      <c r="D585" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B586" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C586" t="inlineStr">
-        <is>
-          <t>diag_FAILED_GROUND_TRUTH_MISSING_KEY</t>
-        </is>
-      </c>
-      <c r="D586" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C587" t="inlineStr">
-        <is>
-          <t>diag_FAILED_API_EXHAUSTED</t>
-        </is>
-      </c>
-      <c r="D587" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B588" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C588" t="inlineStr">
-        <is>
-          <t>diag_FAILED_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D588" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>n_runs</t>
-        </is>
-      </c>
-      <c r="D589" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>n_successful_runs_mean</t>
-        </is>
-      </c>
-      <c r="D590" t="n">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B591" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>n_failed_scenarios</t>
-        </is>
-      </c>
-      <c r="D591" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B592" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>n_total_arch_scenarios</t>
-        </is>
-      </c>
-      <c r="D592" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>total_failure_rate</t>
-        </is>
-      </c>
-      <c r="D593" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>extraction_failure_rate</t>
-        </is>
-      </c>
-      <c r="D594" t="n">
-        <v>0.0051</v>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B595" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>calculation_failure_rate</t>
-        </is>
-      </c>
-      <c r="D595" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>n_extraction_failures</t>
-        </is>
-      </c>
-      <c r="D596" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>n_calculation_failures</t>
-        </is>
-      </c>
-      <c r="D597" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_overall</t>
-        </is>
-      </c>
-      <c r="D598" t="n">
-        <v>0.9202</v>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_pvalue</t>
-        </is>
-      </c>
-      <c r="D599" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C600" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_HVAC</t>
-        </is>
-      </c>
-      <c r="D600" t="n">
-        <v>0.9992</v>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_HVAC_pvalue</t>
-        </is>
-      </c>
-      <c r="D601" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_Appliance</t>
-        </is>
-      </c>
-      <c r="D602" t="n">
-        <v>0.8988</v>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_Appliance_pvalue</t>
-        </is>
-      </c>
-      <c r="D603" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_Shower</t>
-        </is>
-      </c>
-      <c r="D604" t="n">
-        <v>0.9661999999999999</v>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>cross_criterion_rho_Shower_pvalue</t>
-        </is>
-      </c>
-      <c r="D605" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Output Files Qwen3.5 9B/metrics_summary_qwen.xlsx
+++ b/Output Files Qwen3.5 9B/metrics_summary_qwen.xlsx
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1829</v>
+        <v>0.1838</v>
       </c>
     </row>
     <row r="7">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2341</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="8">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2215</v>
+        <v>0.2217</v>
       </c>
     </row>
     <row r="11">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2787</v>
+        <v>0.2785</v>
       </c>
     </row>
     <row r="12">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.2582</v>
+        <v>1.2562</v>
       </c>
     </row>
     <row r="13">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="17">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0.6714</v>
       </c>
     </row>
     <row r="33">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0.5846</v>
       </c>
     </row>
     <row r="49">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.1591</v>
+        <v>0.1621</v>
       </c>
     </row>
     <row r="55">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.2137</v>
+        <v>0.2099</v>
       </c>
     </row>
     <row r="56">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.193</v>
+        <v>0.1938</v>
       </c>
     </row>
     <row r="59">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.25</v>
+        <v>0.2492</v>
       </c>
     </row>
     <row r="60">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.2953</v>
+        <v>1.2859</v>
       </c>
     </row>
     <row r="61">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="65">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.1759</v>
+        <v>0.1742</v>
       </c>
     </row>
     <row r="71">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.2419</v>
+        <v>0.2389</v>
       </c>
     </row>
     <row r="72">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.1752</v>
+        <v>0.1748</v>
       </c>
     </row>
     <row r="75">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.2344</v>
+        <v>0.2336</v>
       </c>
     </row>
     <row r="76">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.3379</v>
+        <v>1.3364</v>
       </c>
     </row>
     <row r="77">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="81">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="97">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>0.8615</v>
       </c>
     </row>
     <row r="113">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.1343</v>
+        <v>0.1288</v>
       </c>
     </row>
     <row r="119">
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.2053</v>
+        <v>0.1934</v>
       </c>
     </row>
     <row r="120">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.1663</v>
+        <v>0.1649</v>
       </c>
     </row>
     <row r="123">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.2214</v>
+        <v>0.2187</v>
       </c>
     </row>
     <row r="124">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1.3313</v>
+        <v>1.3263</v>
       </c>
     </row>
     <row r="125">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>0.7333</v>
       </c>
     </row>
     <row r="129">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0107</v>
       </c>
     </row>
     <row r="135">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.0356</v>
+        <v>0.0373</v>
       </c>
     </row>
     <row r="136">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0682</v>
       </c>
     </row>
     <row r="139">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.1525</v>
+        <v>0.1526</v>
       </c>
     </row>
     <row r="140">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2.2559</v>
+        <v>2.2375</v>
       </c>
     </row>
     <row r="141">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>0.9641</v>
       </c>
     </row>
     <row r="145">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="161">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>0.9692</v>
       </c>
     </row>
     <row r="177">
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0.0271</v>
+        <v>0.0347</v>
       </c>
     </row>
     <row r="183">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0673</v>
       </c>
     </row>
     <row r="184">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0.038</v>
+        <v>0.0399</v>
       </c>
     </row>
     <row r="187">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0.0881</v>
+        <v>0.0887</v>
       </c>
     </row>
     <row r="188">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2.3184</v>
+        <v>2.2231</v>
       </c>
     </row>
     <row r="189">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="193">
